--- a/tiger_audit_springdale_sharonville/reports/TIGER-Audit-Springdale-Sharonville.xlsx
+++ b/tiger_audit_springdale_sharonville/reports/TIGER-Audit-Springdale-Sharonville.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T01:57:49+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:09:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2172,18 +2172,18 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Springfield Pike</t>
+          <t>Tri-County Parkway East</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>0</v>
+      <c r="D8" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2198,18 +2198,18 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Tri-County Parkway East</t>
+          <t>Springfield Pike</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D9" s="10" t="n">
-        <v>4</v>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2276,18 +2276,18 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Mosteller Road</t>
+          <t>West Kemper Road</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>0</v>
+      <c r="D12" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>secondary, tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2302,18 +2302,18 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>West Kemper Road</t>
+          <t>Mosteller Road</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="D13" s="10" t="n">
-        <v>6</v>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>secondary, tertiary</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -2380,18 +2380,18 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Carpenters Run</t>
+          <t>Creek Road</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>8</v>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2406,18 +2406,18 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Creek Road</t>
+          <t>Carpenters Run</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>0</v>
+      <c r="D17" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Grove Road</t>
+          <t>Commons Drive</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Commons Drive</t>
+          <t>Grove Road</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2640,18 +2640,18 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Dixie Court</t>
+          <t>Old Commons Drive</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>0</v>
+      <c r="D26" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>path, residential, service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2692,18 +2692,18 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Lake Forest Drive</t>
+          <t>Dixie Court</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D28" s="10" t="n">
-        <v>5</v>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>path, residential, service</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Old Commons Drive</t>
+          <t>Medallion Drive</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2770,18 +2770,18 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Medallion Drive</t>
+          <t>Lake Forest Drive</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Little Creek Lane</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Gano Road</t>
+          <t>Lippelman Road</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -2848,14 +2848,14 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Lippelman Road</t>
+          <t>Columbia Circle</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D34" s="5" t="n">
-        <v>0</v>
+      <c r="D34" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -2874,14 +2874,14 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Columbia Circle</t>
+          <t>Gano Road</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="10" t="n">
-        <v>2</v>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Little Creek Lane</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Dimmick Road</t>
+          <t>Cornell Road</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Carver Road</t>
+          <t>Century Boulevard</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Cornell Road</t>
+          <t>Carver Road</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Fields Ertel Road</t>
+          <t>Union Centre Boulevard</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D40" s="5" t="n">
-        <v>0</v>
+      <c r="D40" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Century Boulevard</t>
+          <t>Maple Avenue</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -3056,18 +3056,18 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Maple Avenue</t>
+          <t>Linden Boulevard</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="5" t="n">
-        <v>0</v>
+      <c r="D42" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -3082,18 +3082,18 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Allenhurst Boulevard East</t>
+          <t>Mangham Drive</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D43" s="10" t="n">
-        <v>3</v>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -3108,18 +3108,18 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Union Centre Boulevard</t>
+          <t>Allenhurst Boulevard East</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Morse Avenue</t>
+          <t>Dimmick Road</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -3160,18 +3160,18 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Linden Boulevard</t>
+          <t>Oak Road</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D46" s="10" t="n">
-        <v>3</v>
+      <c r="D46" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service, tertiary</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -3186,18 +3186,18 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Oak Road</t>
+          <t>Brandywine Drive</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D47" s="5" t="n">
-        <v>0</v>
+      <c r="D47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>residential, service, tertiary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -3212,18 +3212,18 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Brandywine Drive</t>
+          <t>Morse Avenue</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D48" s="10" t="n">
-        <v>1</v>
+      <c r="D48" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Mangham Drive</t>
+          <t>Buckeye Falls Drive</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>service</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Buckeye Falls Drive</t>
+          <t>Fields Ertel Road</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -59950,12 +59950,14 @@
           <t>Blue Ash / Montgomery</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>NOT STARTED</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr"/>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>AUDIT COMPLETE</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>1934</v>
+      </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Blue Ash, Montgomery, Deer Park, Silverton, Kenwood, Madeira</t>
@@ -59988,12 +59990,14 @@
           <t>Northgate / Mt. Healthy</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>NOT STARTED</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr"/>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>AUDIT COMPLETE</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1664</v>
+      </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Mt. Healthy, North College Hill, Finneytown, Northgate</t>
@@ -60006,12 +60010,14 @@
           <t>Forest Park / Pleasant Run</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>NOT STARTED</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>AUDIT COMPLETE</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2066</v>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Forest Park, Pleasant Run, Greenhills</t>
@@ -60215,7 +60221,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T01:57:49+00:00</t>
+          <t>2026-04-29T02:09:51+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_springdale_sharonville/reports/TIGER-Audit-Springdale-Sharonville.xlsx
+++ b/tiger_audit_springdale_sharonville/reports/TIGER-Audit-Springdale-Sharonville.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:09:51+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:18:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2432,18 +2432,18 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Kemper Commons Circle</t>
+          <t>Northland Boulevard</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -2458,18 +2458,18 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Northland Boulevard</t>
+          <t>Kemper Commons Circle</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2484,14 +2484,14 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Tri-County Parkway</t>
+          <t>Plainfield Road</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D20" s="5" t="n">
-        <v>0</v>
+      <c r="D20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -2510,14 +2510,14 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Plainfield Road</t>
+          <t>Tri-County Parkway</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D21" s="10" t="n">
-        <v>4</v>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Commons Drive</t>
+          <t>Grove Road</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2588,18 +2588,18 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Grove Road</t>
+          <t>Commerce Boulevard</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D24" s="5" t="n">
-        <v>0</v>
+      <c r="D24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2614,18 +2614,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Commerce Boulevard</t>
+          <t>Commons Drive</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D25" s="10" t="n">
-        <v>4</v>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2640,14 +2640,14 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Old Commons Drive</t>
+          <t>Lake Forest Drive</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -2666,18 +2666,18 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Evendale Drive</t>
+          <t>Old Commons Drive</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D27" s="5" t="n">
-        <v>0</v>
+      <c r="D27" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2718,18 +2718,18 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Medallion Drive</t>
+          <t>Evendale Drive</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D29" s="10" t="n">
-        <v>2</v>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2770,18 +2770,18 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Lake Forest Drive</t>
+          <t>Medallion Drive</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Columbia Circle</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Columbia Circle</t>
+          <t>Little Creek Lane</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2874,18 +2874,18 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Gano Road</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="5" t="n">
-        <v>0</v>
+      <c r="D35" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -2900,18 +2900,18 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Little Creek Lane</t>
+          <t>Gano Road</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="10" t="n">
-        <v>2</v>
+      <c r="D36" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Cornell Road</t>
+          <t>Buckeye Falls Drive</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>service</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Carver Road</t>
+          <t>Morse Avenue</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -3004,18 +3004,18 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Union Centre Boulevard</t>
+          <t>Dimmick Road</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D40" s="10" t="n">
-        <v>5</v>
+      <c r="D40" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Maple Avenue</t>
+          <t>Cornell Road</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -3056,18 +3056,18 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Linden Boulevard</t>
+          <t>Union Centre Boulevard</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -3082,18 +3082,18 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Mangham Drive</t>
+          <t>Brandywine Drive</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D43" s="5" t="n">
-        <v>0</v>
+      <c r="D43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -3108,18 +3108,18 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Allenhurst Boulevard East</t>
+          <t>Oak Road</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="10" t="n">
-        <v>3</v>
+      <c r="D44" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service, tertiary</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -3134,18 +3134,18 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Dimmick Road</t>
+          <t>Linden Boulevard</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D45" s="5" t="n">
-        <v>0</v>
+      <c r="D45" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Oak Road</t>
+          <t>Mangham Drive</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>residential, service, tertiary</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -3186,18 +3186,18 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Brandywine Drive</t>
+          <t>Carver Road</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D47" s="10" t="n">
-        <v>1</v>
+      <c r="D47" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Morse Avenue</t>
+          <t>Maple Avenue</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Buckeye Falls Drive</t>
+          <t>Fields Ertel Road</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -3264,18 +3264,18 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Fields Ertel Road</t>
+          <t>Allenhurst Boulevard East</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D50" s="5" t="n">
-        <v>0</v>
+      <c r="D50" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -60221,7 +60221,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:09:51+00:00</t>
+          <t>2026-04-29T02:18:32+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_springdale_sharonville/reports/TIGER-Audit-Springdale-Sharonville.xlsx
+++ b/tiger_audit_springdale_sharonville/reports/TIGER-Audit-Springdale-Sharonville.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:18:32+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:34:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Chester Road</t>
+          <t>Mulhauser Road</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>residential, secondary, tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Mulhauser Road</t>
+          <t>Chester Road</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential, secondary, tertiary</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2172,18 +2172,18 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Tri-County Parkway East</t>
+          <t>Springfield Pike</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D8" s="10" t="n">
-        <v>4</v>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2198,18 +2198,18 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Springfield Pike</t>
+          <t>Tri-County Parkway East</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>0</v>
+      <c r="D9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2276,18 +2276,18 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>West Kemper Road</t>
+          <t>Mosteller Road</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="D12" s="10" t="n">
-        <v>6</v>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>secondary, tertiary</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2302,18 +2302,18 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Mosteller Road</t>
+          <t>West Kemper Road</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>0</v>
+      <c r="D13" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>secondary, tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -2380,18 +2380,18 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Creek Road</t>
+          <t>Carpenters Run</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>0</v>
+      <c r="D16" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2406,18 +2406,18 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Carpenters Run</t>
+          <t>Creek Road</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D17" s="10" t="n">
-        <v>8</v>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2484,14 +2484,14 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Plainfield Road</t>
+          <t>Tri-County Parkway</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D20" s="10" t="n">
-        <v>4</v>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -2510,14 +2510,14 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Tri-County Parkway</t>
+          <t>Plainfield Road</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D21" s="5" t="n">
-        <v>0</v>
+      <c r="D21" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Grove Road</t>
+          <t>Commons Drive</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Commons Drive</t>
+          <t>Grove Road</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2640,18 +2640,18 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Lake Forest Drive</t>
+          <t>Medallion Drive</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2666,18 +2666,18 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Old Commons Drive</t>
+          <t>Evendale Drive</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>2</v>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2692,18 +2692,18 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Dixie Court</t>
+          <t>Lake Forest Drive</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D28" s="5" t="n">
-        <v>0</v>
+      <c r="D28" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>path, residential, service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Evendale Drive</t>
+          <t>Hauck Road</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2744,14 +2744,14 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Hauck Road</t>
+          <t>Old Commons Drive</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D30" s="5" t="n">
-        <v>0</v>
+      <c r="D30" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -2770,18 +2770,18 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Medallion Drive</t>
+          <t>Dixie Court</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D31" s="10" t="n">
-        <v>2</v>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>path, residential, service</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2796,14 +2796,14 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Columbia Circle</t>
+          <t>Lippelman Road</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D32" s="10" t="n">
-        <v>2</v>
+      <c r="D32" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Lippelman Road</t>
+          <t>Gano Road</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Columbia Circle</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -2900,18 +2900,18 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Gano Road</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="5" t="n">
-        <v>0</v>
+      <c r="D36" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Buckeye Falls Drive</t>
+          <t>Fields Ertel Road</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Century Boulevard</t>
+          <t>Morse Avenue</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
@@ -2978,14 +2978,14 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Morse Avenue</t>
+          <t>Allenhurst Boulevard East</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D39" s="5" t="n">
-        <v>0</v>
+      <c r="D39" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Cornell Road</t>
+          <t>Century Boulevard</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -3056,18 +3056,18 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Union Centre Boulevard</t>
+          <t>Cornell Road</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="10" t="n">
-        <v>5</v>
+      <c r="D42" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -3082,18 +3082,18 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Brandywine Drive</t>
+          <t>Carver Road</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D43" s="10" t="n">
-        <v>1</v>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Mangham Drive</t>
+          <t>Maple Avenue</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Carver Road</t>
+          <t>Buckeye Falls Drive</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>service</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -3212,14 +3212,14 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Maple Avenue</t>
+          <t>Brandywine Drive</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D48" s="5" t="n">
-        <v>0</v>
+      <c r="D48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
@@ -3238,14 +3238,14 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Fields Ertel Road</t>
+          <t>Union Centre Boulevard</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D49" s="5" t="n">
-        <v>0</v>
+      <c r="D49" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
@@ -3264,18 +3264,18 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Allenhurst Boulevard East</t>
+          <t>Mangham Drive</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D50" s="10" t="n">
-        <v>3</v>
+      <c r="D50" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -60221,7 +60221,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:18:32+00:00</t>
+          <t>2026-04-29T02:34:00+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_springdale_sharonville/reports/TIGER-Audit-Springdale-Sharonville.xlsx
+++ b/tiger_audit_springdale_sharonville/reports/TIGER-Audit-Springdale-Sharonville.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:34:00+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:42:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2172,18 +2172,18 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Springfield Pike</t>
+          <t>Tri-County Parkway East</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>0</v>
+      <c r="D8" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2198,18 +2198,18 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Tri-County Parkway East</t>
+          <t>Springfield Pike</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D9" s="10" t="n">
-        <v>4</v>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2276,18 +2276,18 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Mosteller Road</t>
+          <t>West Kemper Road</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>0</v>
+      <c r="D12" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>secondary, tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2302,18 +2302,18 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>West Kemper Road</t>
+          <t>Mosteller Road</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="D13" s="10" t="n">
-        <v>6</v>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>secondary, tertiary</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -2380,18 +2380,18 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Carpenters Run</t>
+          <t>Creek Road</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>8</v>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2406,18 +2406,18 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Creek Road</t>
+          <t>Carpenters Run</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>0</v>
+      <c r="D17" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2432,18 +2432,18 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Northland Boulevard</t>
+          <t>Kemper Commons Circle</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -2458,18 +2458,18 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Kemper Commons Circle</t>
+          <t>Northland Boulevard</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2484,14 +2484,14 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Tri-County Parkway</t>
+          <t>Plainfield Road</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D20" s="5" t="n">
-        <v>0</v>
+      <c r="D20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -2510,14 +2510,14 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Plainfield Road</t>
+          <t>Tri-County Parkway</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D21" s="10" t="n">
-        <v>4</v>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Commons Drive</t>
+          <t>Grove Road</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2588,18 +2588,18 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Commerce Boulevard</t>
+          <t>Commons Drive</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D24" s="10" t="n">
-        <v>4</v>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2614,18 +2614,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Grove Road</t>
+          <t>Commerce Boulevard</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
+      <c r="D25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2640,18 +2640,18 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Medallion Drive</t>
+          <t>Lake Forest Drive</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Evendale Drive</t>
+          <t>Hauck Road</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2692,18 +2692,18 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Lake Forest Drive</t>
+          <t>Medallion Drive</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Hauck Road</t>
+          <t>Dixie Court</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>path, residential, service</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Dixie Court</t>
+          <t>Evendale Drive</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>path, residential, service</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Lippelman Road</t>
+          <t>Gano Road</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -2822,18 +2822,18 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Gano Road</t>
+          <t>Little Creek Lane</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D33" s="5" t="n">
-        <v>0</v>
+      <c r="D33" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Little Creek Lane</t>
+          <t>Columbia Circle</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2874,14 +2874,14 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Columbia Circle</t>
+          <t>Lippelman Road</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="10" t="n">
-        <v>2</v>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -2926,18 +2926,18 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Fields Ertel Road</t>
+          <t>Allenhurst Boulevard East</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="5" t="n">
-        <v>0</v>
+      <c r="D37" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Morse Avenue</t>
+          <t>Maple Avenue</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -2978,18 +2978,18 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Allenhurst Boulevard East</t>
+          <t>Brandywine Drive</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Dimmick Road</t>
+          <t>Morse Avenue</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Century Boulevard</t>
+          <t>Oak Road</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service, tertiary</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Cornell Road</t>
+          <t>Fields Ertel Road</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Carver Road</t>
+          <t>Mangham Drive</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Oak Road</t>
+          <t>Century Boulevard</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>residential, service, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -3134,18 +3134,18 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Linden Boulevard</t>
+          <t>Buckeye Falls Drive</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D45" s="10" t="n">
-        <v>3</v>
+      <c r="D45" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>service</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Maple Avenue</t>
+          <t>Carver Road</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -3186,18 +3186,18 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Buckeye Falls Drive</t>
+          <t>Linden Boulevard</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D47" s="5" t="n">
-        <v>0</v>
+      <c r="D47" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -3212,18 +3212,18 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Brandywine Drive</t>
+          <t>Cornell Road</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D48" s="10" t="n">
-        <v>1</v>
+      <c r="D48" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -3238,18 +3238,18 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Union Centre Boulevard</t>
+          <t>Dimmick Road</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D49" s="10" t="n">
-        <v>5</v>
+      <c r="D49" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -3264,18 +3264,18 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Mangham Drive</t>
+          <t>Union Centre Boulevard</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D50" s="5" t="n">
-        <v>0</v>
+      <c r="D50" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -60221,7 +60221,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:34:00+00:00</t>
+          <t>2026-04-29T02:42:04+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_springdale_sharonville/reports/TIGER-Audit-Springdale-Sharonville.xlsx
+++ b/tiger_audit_springdale_sharonville/reports/TIGER-Audit-Springdale-Sharonville.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:42:04+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:49:17+00:00</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Mulhauser Road</t>
+          <t>Chester Road</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential, secondary, tertiary</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Chester Road</t>
+          <t>Mulhauser Road</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>residential, secondary, tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2172,18 +2172,18 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Tri-County Parkway East</t>
+          <t>Springfield Pike</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D8" s="10" t="n">
-        <v>4</v>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2198,18 +2198,18 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Springfield Pike</t>
+          <t>Tri-County Parkway East</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>0</v>
+      <c r="D9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Grove Road</t>
+          <t>Commons Drive</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2588,18 +2588,18 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Commons Drive</t>
+          <t>Commerce Boulevard</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D24" s="5" t="n">
-        <v>0</v>
+      <c r="D24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2614,18 +2614,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Commerce Boulevard</t>
+          <t>Grove Road</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D25" s="10" t="n">
-        <v>4</v>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2640,18 +2640,18 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Lake Forest Drive</t>
+          <t>Dixie Court</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>5</v>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>path, residential, service</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Medallion Drive</t>
+          <t>Old Commons Drive</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Dixie Court</t>
+          <t>Evendale Drive</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>path, residential, service</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2744,14 +2744,14 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Old Commons Drive</t>
+          <t>Lake Forest Drive</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -2770,18 +2770,18 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Evendale Drive</t>
+          <t>Medallion Drive</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D31" s="5" t="n">
-        <v>0</v>
+      <c r="D31" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2796,18 +2796,18 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Gano Road</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D32" s="5" t="n">
-        <v>0</v>
+      <c r="D32" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Little Creek Lane</t>
+          <t>Columbia Circle</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2848,14 +2848,14 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Columbia Circle</t>
+          <t>Lippelman Road</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D34" s="10" t="n">
-        <v>2</v>
+      <c r="D34" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Lippelman Road</t>
+          <t>Gano Road</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Little Creek Lane</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -2926,14 +2926,14 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Allenhurst Boulevard East</t>
+          <t>Century Boulevard</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="10" t="n">
-        <v>3</v>
+      <c r="D37" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Maple Avenue</t>
+          <t>Cornell Road</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -2978,18 +2978,18 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Brandywine Drive</t>
+          <t>Carver Road</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D39" s="10" t="n">
-        <v>1</v>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Morse Avenue</t>
+          <t>Buckeye Falls Drive</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>service</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Oak Road</t>
+          <t>Morse Avenue</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>residential, service, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Fields Ertel Road</t>
+          <t>Dimmick Road</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -3082,18 +3082,18 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Mangham Drive</t>
+          <t>Allenhurst Boulevard East</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D43" s="5" t="n">
-        <v>0</v>
+      <c r="D43" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -3108,18 +3108,18 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Century Boulevard</t>
+          <t>Union Centre Boulevard</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="5" t="n">
-        <v>0</v>
+      <c r="D44" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -3134,18 +3134,18 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Buckeye Falls Drive</t>
+          <t>Brandywine Drive</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D45" s="5" t="n">
-        <v>0</v>
+      <c r="D45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Carver Road</t>
+          <t>Maple Avenue</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -3186,18 +3186,18 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Linden Boulevard</t>
+          <t>Mangham Drive</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D47" s="10" t="n">
-        <v>3</v>
+      <c r="D47" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -3212,18 +3212,18 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Cornell Road</t>
+          <t>Linden Boulevard</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D48" s="5" t="n">
-        <v>0</v>
+      <c r="D48" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Dimmick Road</t>
+          <t>Oak Road</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, service, tertiary</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -3264,14 +3264,14 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Union Centre Boulevard</t>
+          <t>Fields Ertel Road</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D50" s="10" t="n">
-        <v>5</v>
+      <c r="D50" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
@@ -60221,7 +60221,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:42:04+00:00</t>
+          <t>2026-04-29T02:49:17+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_springdale_sharonville/reports/TIGER-Audit-Springdale-Sharonville.xlsx
+++ b/tiger_audit_springdale_sharonville/reports/TIGER-Audit-Springdale-Sharonville.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:49:17+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T13:07:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2432,18 +2432,18 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Kemper Commons Circle</t>
+          <t>Northland Boulevard</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -2458,18 +2458,18 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Northland Boulevard</t>
+          <t>Kemper Commons Circle</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2484,14 +2484,14 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Plainfield Road</t>
+          <t>Tri-County Parkway</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D20" s="10" t="n">
-        <v>4</v>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -2510,14 +2510,14 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Tri-County Parkway</t>
+          <t>Plainfield Road</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D21" s="5" t="n">
-        <v>0</v>
+      <c r="D21" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Commons Drive</t>
+          <t>Grove Road</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2588,18 +2588,18 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Commerce Boulevard</t>
+          <t>Commons Drive</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D24" s="10" t="n">
-        <v>4</v>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2614,18 +2614,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Grove Road</t>
+          <t>Commerce Boulevard</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
+      <c r="D25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2640,18 +2640,18 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Dixie Court</t>
+          <t>Old Commons Drive</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>0</v>
+      <c r="D26" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>path, residential, service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Hauck Road</t>
+          <t>Lake Forest Drive</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D27" s="5" t="n">
-        <v>0</v>
+      <c r="D27" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -2692,18 +2692,18 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Old Commons Drive</t>
+          <t>Evendale Drive</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D28" s="10" t="n">
-        <v>2</v>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2718,18 +2718,18 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Evendale Drive</t>
+          <t>Medallion Drive</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D29" s="5" t="n">
-        <v>0</v>
+      <c r="D29" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2744,14 +2744,14 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Lake Forest Drive</t>
+          <t>Hauck Road</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D30" s="10" t="n">
-        <v>5</v>
+      <c r="D30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -2770,18 +2770,18 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Medallion Drive</t>
+          <t>Dixie Court</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D31" s="10" t="n">
-        <v>2</v>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>path, residential, service</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2796,18 +2796,18 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Lippelman Road</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D32" s="10" t="n">
-        <v>2</v>
+      <c r="D32" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2822,14 +2822,14 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Columbia Circle</t>
+          <t>Gano Road</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D33" s="10" t="n">
-        <v>2</v>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -2848,14 +2848,14 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Lippelman Road</t>
+          <t>Columbia Circle</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D34" s="5" t="n">
-        <v>0</v>
+      <c r="D34" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -2874,18 +2874,18 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Gano Road</t>
+          <t>Little Creek Lane</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="5" t="n">
-        <v>0</v>
+      <c r="D35" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Little Creek Lane</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Century Boulevard</t>
+          <t>Maple Avenue</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -2952,18 +2952,18 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Cornell Road</t>
+          <t>Union Centre Boulevard</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="5" t="n">
-        <v>0</v>
+      <c r="D38" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Carver Road</t>
+          <t>Fields Ertel Road</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Buckeye Falls Drive</t>
+          <t>Dimmick Road</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -3030,18 +3030,18 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Morse Avenue</t>
+          <t>Brandywine Drive</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D41" s="5" t="n">
-        <v>0</v>
+      <c r="D41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -3056,18 +3056,18 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Dimmick Road</t>
+          <t>Linden Boulevard</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="5" t="n">
-        <v>0</v>
+      <c r="D42" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -3082,18 +3082,18 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Allenhurst Boulevard East</t>
+          <t>Buckeye Falls Drive</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D43" s="10" t="n">
-        <v>3</v>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>service</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -3108,18 +3108,18 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Union Centre Boulevard</t>
+          <t>Morse Avenue</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="10" t="n">
-        <v>5</v>
+      <c r="D44" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -3134,18 +3134,18 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Brandywine Drive</t>
+          <t>Carver Road</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D45" s="10" t="n">
-        <v>1</v>
+      <c r="D45" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Maple Avenue</t>
+          <t>Cornell Road</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -3212,18 +3212,18 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Linden Boulevard</t>
+          <t>Oak Road</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D48" s="10" t="n">
-        <v>3</v>
+      <c r="D48" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service, tertiary</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -3238,18 +3238,18 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Oak Road</t>
+          <t>Allenhurst Boulevard East</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D49" s="5" t="n">
-        <v>0</v>
+      <c r="D49" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>residential, service, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Fields Ertel Road</t>
+          <t>Century Boulevard</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -60221,7 +60221,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:49:17+00:00</t>
+          <t>2026-04-29T13:07:56+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_springdale_sharonville/reports/TIGER-Audit-Springdale-Sharonville.xlsx
+++ b/tiger_audit_springdale_sharonville/reports/TIGER-Audit-Springdale-Sharonville.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T13:07:56+00:00</t>
+          <t>Audit date (UTC): 2026-04-30T17:05:35+00:00</t>
         </is>
       </c>
     </row>
@@ -2276,18 +2276,18 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>West Kemper Road</t>
+          <t>Mosteller Road</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="D12" s="10" t="n">
-        <v>6</v>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>secondary, tertiary</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2302,18 +2302,18 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Mosteller Road</t>
+          <t>West Kemper Road</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>0</v>
+      <c r="D13" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>secondary, tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -2380,18 +2380,18 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Creek Road</t>
+          <t>Carpenters Run</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>0</v>
+      <c r="D16" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2406,18 +2406,18 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Carpenters Run</t>
+          <t>Creek Road</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D17" s="10" t="n">
-        <v>8</v>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2484,14 +2484,14 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Tri-County Parkway</t>
+          <t>Plainfield Road</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D20" s="5" t="n">
-        <v>0</v>
+      <c r="D20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -2510,14 +2510,14 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Plainfield Road</t>
+          <t>Tri-County Parkway</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D21" s="10" t="n">
-        <v>4</v>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -2640,14 +2640,14 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Old Commons Drive</t>
+          <t>Hauck Road</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>2</v>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -2666,18 +2666,18 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Lake Forest Drive</t>
+          <t>Medallion Drive</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2692,18 +2692,18 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Evendale Drive</t>
+          <t>Lake Forest Drive</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D28" s="5" t="n">
-        <v>0</v>
+      <c r="D28" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2718,18 +2718,18 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Medallion Drive</t>
+          <t>Evendale Drive</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D29" s="10" t="n">
-        <v>2</v>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Hauck Road</t>
+          <t>Dixie Court</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>path, residential, service</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2770,18 +2770,18 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Dixie Court</t>
+          <t>Old Commons Drive</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D31" s="5" t="n">
-        <v>0</v>
+      <c r="D31" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>path, residential, service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2822,18 +2822,18 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Gano Road</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D33" s="5" t="n">
-        <v>0</v>
+      <c r="D33" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Columbia Circle</t>
+          <t>Little Creek Lane</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2874,18 +2874,18 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Little Creek Lane</t>
+          <t>Gano Road</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="10" t="n">
-        <v>2</v>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Columbia Circle</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Maple Avenue</t>
+          <t>Cornell Road</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -2952,14 +2952,14 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Union Centre Boulevard</t>
+          <t>Fields Ertel Road</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="10" t="n">
-        <v>5</v>
+      <c r="D38" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Fields Ertel Road</t>
+          <t>Century Boulevard</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Dimmick Road</t>
+          <t>Carver Road</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -3030,18 +3030,18 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Brandywine Drive</t>
+          <t>Union Centre Boulevard</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -3056,18 +3056,18 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Linden Boulevard</t>
+          <t>Oak Road</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="10" t="n">
-        <v>3</v>
+      <c r="D42" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service, tertiary</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -3082,18 +3082,18 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Buckeye Falls Drive</t>
+          <t>Allenhurst Boulevard East</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D43" s="5" t="n">
-        <v>0</v>
+      <c r="D43" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Morse Avenue</t>
+          <t>Mangham Drive</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -3134,18 +3134,18 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Carver Road</t>
+          <t>Brandywine Drive</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D45" s="5" t="n">
-        <v>0</v>
+      <c r="D45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Cornell Road</t>
+          <t>Buckeye Falls Drive</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>service</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Mangham Drive</t>
+          <t>Dimmick Road</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -3212,18 +3212,18 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Oak Road</t>
+          <t>Linden Boulevard</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D48" s="5" t="n">
-        <v>0</v>
+      <c r="D48" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>residential, service, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -3238,18 +3238,18 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Allenhurst Boulevard East</t>
+          <t>Maple Avenue</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D49" s="10" t="n">
-        <v>3</v>
+      <c r="D49" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Century Boulevard</t>
+          <t>Morse Avenue</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
@@ -60221,7 +60221,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T13:07:56+00:00</t>
+          <t>2026-04-30T17:05:35+00:00</t>
         </is>
       </c>
     </row>
